--- a/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -725,25 +725,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>46000</v>
+        <v>46200</v>
       </c>
       <c r="E8" s="3">
-        <v>23900</v>
+        <v>24000</v>
       </c>
       <c r="F8" s="3">
         <v>15300</v>
       </c>
       <c r="G8" s="3">
-        <v>87300</v>
+        <v>87500</v>
       </c>
       <c r="H8" s="3">
-        <v>112600</v>
+        <v>112900</v>
       </c>
       <c r="I8" s="3">
-        <v>147300</v>
+        <v>147700</v>
       </c>
       <c r="J8" s="3">
-        <v>112600</v>
+        <v>112800</v>
       </c>
       <c r="K8" s="3">
         <v>100900</v>
@@ -767,7 +767,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E9" s="3">
         <v>1900</v>
@@ -776,16 +776,16 @@
         <v>300</v>
       </c>
       <c r="G9" s="3">
-        <v>35200</v>
+        <v>35300</v>
       </c>
       <c r="H9" s="3">
-        <v>51500</v>
+        <v>51700</v>
       </c>
       <c r="I9" s="3">
-        <v>59300</v>
+        <v>59500</v>
       </c>
       <c r="J9" s="3">
-        <v>50300</v>
+        <v>50400</v>
       </c>
       <c r="K9" s="3">
         <v>50300</v>
@@ -809,25 +809,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>38000</v>
+        <v>38100</v>
       </c>
       <c r="E10" s="3">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="F10" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="G10" s="3">
-        <v>52200</v>
+        <v>52300</v>
       </c>
       <c r="H10" s="3">
-        <v>61100</v>
+        <v>61200</v>
       </c>
       <c r="I10" s="3">
-        <v>88000</v>
+        <v>88300</v>
       </c>
       <c r="J10" s="3">
-        <v>62300</v>
+        <v>62400</v>
       </c>
       <c r="K10" s="3">
         <v>50500</v>
@@ -956,7 +956,7 @@
         <v>300</v>
       </c>
       <c r="E14" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F14" s="3">
         <v>3200</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>51000</v>
+        <v>51200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1052,25 +1052,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>45400</v>
+        <v>45500</v>
       </c>
       <c r="E17" s="3">
-        <v>29800</v>
+        <v>29900</v>
       </c>
       <c r="F17" s="3">
-        <v>33000</v>
+        <v>33100</v>
       </c>
       <c r="G17" s="3">
-        <v>94800</v>
+        <v>95100</v>
       </c>
       <c r="H17" s="3">
-        <v>143600</v>
+        <v>144000</v>
       </c>
       <c r="I17" s="3">
-        <v>187800</v>
+        <v>188200</v>
       </c>
       <c r="J17" s="3">
-        <v>186000</v>
+        <v>186500</v>
       </c>
       <c r="K17" s="3">
         <v>115500</v>
@@ -1106,13 +1106,13 @@
         <v>-7500</v>
       </c>
       <c r="H18" s="3">
-        <v>-31000</v>
+        <v>-31100</v>
       </c>
       <c r="I18" s="3">
-        <v>-40400</v>
+        <v>-40500</v>
       </c>
       <c r="J18" s="3">
-        <v>-73500</v>
+        <v>-73600</v>
       </c>
       <c r="K18" s="3">
         <v>-14600</v>
@@ -1211,10 +1211,10 @@
         <v>-5000</v>
       </c>
       <c r="I21" s="3">
-        <v>-41500</v>
+        <v>-41600</v>
       </c>
       <c r="J21" s="3">
-        <v>-66700</v>
+        <v>-66800</v>
       </c>
       <c r="K21" s="3">
         <v>-11400</v>
@@ -1295,10 +1295,10 @@
         <v>-13800</v>
       </c>
       <c r="I23" s="3">
-        <v>-48100</v>
+        <v>-48200</v>
       </c>
       <c r="J23" s="3">
-        <v>-70900</v>
+        <v>-71100</v>
       </c>
       <c r="K23" s="3">
         <v>-15000</v>
@@ -1421,10 +1421,10 @@
         <v>-14400</v>
       </c>
       <c r="I26" s="3">
-        <v>-48700</v>
+        <v>-48900</v>
       </c>
       <c r="J26" s="3">
-        <v>-71400</v>
+        <v>-71600</v>
       </c>
       <c r="K26" s="3">
         <v>-15000</v>
@@ -1451,22 +1451,22 @@
         <v>-3500</v>
       </c>
       <c r="E27" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="F27" s="3">
         <v>-14200</v>
       </c>
       <c r="G27" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="H27" s="3">
         <v>-13800</v>
       </c>
       <c r="I27" s="3">
-        <v>-48000</v>
+        <v>-48200</v>
       </c>
       <c r="J27" s="3">
-        <v>-71000</v>
+        <v>-71200</v>
       </c>
       <c r="K27" s="3">
         <v>-14700</v>
@@ -1703,22 +1703,22 @@
         <v>-3500</v>
       </c>
       <c r="E33" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="F33" s="3">
         <v>-14200</v>
       </c>
       <c r="G33" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="H33" s="3">
         <v>-13800</v>
       </c>
       <c r="I33" s="3">
-        <v>-48000</v>
+        <v>-48200</v>
       </c>
       <c r="J33" s="3">
-        <v>-71000</v>
+        <v>-71200</v>
       </c>
       <c r="K33" s="3">
         <v>-14700</v>
@@ -1787,22 +1787,22 @@
         <v>-3500</v>
       </c>
       <c r="E35" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="F35" s="3">
         <v>-14200</v>
       </c>
       <c r="G35" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="H35" s="3">
         <v>-13800</v>
       </c>
       <c r="I35" s="3">
-        <v>-48000</v>
+        <v>-48200</v>
       </c>
       <c r="J35" s="3">
-        <v>-71000</v>
+        <v>-71200</v>
       </c>
       <c r="K35" s="3">
         <v>-14700</v>
@@ -1912,22 +1912,22 @@
         <v>6100</v>
       </c>
       <c r="E41" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="F41" s="3">
         <v>20600</v>
       </c>
       <c r="G41" s="3">
-        <v>16400</v>
+        <v>16500</v>
       </c>
       <c r="H41" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="I41" s="3">
         <v>29700</v>
       </c>
       <c r="J41" s="3">
-        <v>18400</v>
+        <v>18500</v>
       </c>
       <c r="K41" s="3">
         <v>3200</v>
@@ -1993,7 +1993,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>41100</v>
+        <v>41200</v>
       </c>
       <c r="E43" s="3">
         <v>26300</v>
@@ -2002,16 +2002,16 @@
         <v>14100</v>
       </c>
       <c r="G43" s="3">
-        <v>34900</v>
+        <v>35000</v>
       </c>
       <c r="H43" s="3">
-        <v>65800</v>
+        <v>65900</v>
       </c>
       <c r="I43" s="3">
-        <v>52600</v>
+        <v>52800</v>
       </c>
       <c r="J43" s="3">
-        <v>27500</v>
+        <v>27600</v>
       </c>
       <c r="K43" s="3">
         <v>23400</v>
@@ -2092,7 +2092,7 @@
         <v>10200</v>
       </c>
       <c r="I45" s="3">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="J45" s="3">
         <v>8700</v>
@@ -2119,25 +2119,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>65900</v>
+        <v>66000</v>
       </c>
       <c r="E46" s="3">
-        <v>50300</v>
+        <v>50500</v>
       </c>
       <c r="F46" s="3">
-        <v>49300</v>
+        <v>49400</v>
       </c>
       <c r="G46" s="3">
-        <v>73400</v>
+        <v>73600</v>
       </c>
       <c r="H46" s="3">
-        <v>116900</v>
+        <v>117200</v>
       </c>
       <c r="I46" s="3">
-        <v>106500</v>
+        <v>106700</v>
       </c>
       <c r="J46" s="3">
-        <v>91600</v>
+        <v>91900</v>
       </c>
       <c r="K46" s="3">
         <v>43800</v>
@@ -2248,7 +2248,7 @@
         <v>9400</v>
       </c>
       <c r="E49" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="F49" s="3">
         <v>10700</v>
@@ -2257,7 +2257,7 @@
         <v>20500</v>
       </c>
       <c r="H49" s="3">
-        <v>26900</v>
+        <v>27000</v>
       </c>
       <c r="I49" s="3">
         <v>26800</v>
@@ -2383,7 +2383,7 @@
         <v>3900</v>
       </c>
       <c r="H52" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="I52" s="3">
         <v>2800</v>
@@ -2455,25 +2455,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>81400</v>
+        <v>81600</v>
       </c>
       <c r="E54" s="3">
-        <v>65700</v>
+        <v>65900</v>
       </c>
       <c r="F54" s="3">
-        <v>69100</v>
+        <v>69300</v>
       </c>
       <c r="G54" s="3">
-        <v>105400</v>
+        <v>105600</v>
       </c>
       <c r="H54" s="3">
-        <v>151000</v>
+        <v>151400</v>
       </c>
       <c r="I54" s="3">
-        <v>139700</v>
+        <v>140100</v>
       </c>
       <c r="J54" s="3">
-        <v>115200</v>
+        <v>115500</v>
       </c>
       <c r="K54" s="3">
         <v>64700</v>
@@ -2536,22 +2536,22 @@
         <v>26200</v>
       </c>
       <c r="E57" s="3">
-        <v>28800</v>
+        <v>28900</v>
       </c>
       <c r="F57" s="3">
         <v>26700</v>
       </c>
       <c r="G57" s="3">
-        <v>34400</v>
+        <v>34500</v>
       </c>
       <c r="H57" s="3">
-        <v>63300</v>
+        <v>63500</v>
       </c>
       <c r="I57" s="3">
-        <v>60700</v>
+        <v>60900</v>
       </c>
       <c r="J57" s="3">
-        <v>37900</v>
+        <v>38000</v>
       </c>
       <c r="K57" s="3">
         <v>24800</v>
@@ -2575,7 +2575,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>28600</v>
+        <v>28700</v>
       </c>
       <c r="E58" s="3">
         <v>4700</v>
@@ -2617,7 +2617,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14600</v>
+        <v>14700</v>
       </c>
       <c r="E59" s="3">
         <v>16800</v>
@@ -2626,16 +2626,16 @@
         <v>12700</v>
       </c>
       <c r="G59" s="3">
-        <v>30200</v>
+        <v>30300</v>
       </c>
       <c r="H59" s="3">
-        <v>42200</v>
+        <v>42300</v>
       </c>
       <c r="I59" s="3">
-        <v>62800</v>
+        <v>62900</v>
       </c>
       <c r="J59" s="3">
-        <v>32100</v>
+        <v>32200</v>
       </c>
       <c r="K59" s="3">
         <v>16200</v>
@@ -2659,25 +2659,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>69500</v>
+        <v>69600</v>
       </c>
       <c r="E60" s="3">
-        <v>50300</v>
+        <v>50500</v>
       </c>
       <c r="F60" s="3">
-        <v>41700</v>
+        <v>41800</v>
       </c>
       <c r="G60" s="3">
-        <v>77100</v>
+        <v>77300</v>
       </c>
       <c r="H60" s="3">
-        <v>119400</v>
+        <v>119700</v>
       </c>
       <c r="I60" s="3">
-        <v>129400</v>
+        <v>129800</v>
       </c>
       <c r="J60" s="3">
-        <v>70200</v>
+        <v>70300</v>
       </c>
       <c r="K60" s="3">
         <v>42200</v>
@@ -2710,7 +2710,7 @@
         <v>5200</v>
       </c>
       <c r="G61" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="H61" s="3">
         <v>300</v>
@@ -2911,25 +2911,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>72900</v>
+        <v>73100</v>
       </c>
       <c r="E66" s="3">
-        <v>55000</v>
+        <v>55200</v>
       </c>
       <c r="F66" s="3">
-        <v>55200</v>
+        <v>55300</v>
       </c>
       <c r="G66" s="3">
-        <v>87400</v>
+        <v>87600</v>
       </c>
       <c r="H66" s="3">
-        <v>122600</v>
+        <v>122900</v>
       </c>
       <c r="I66" s="3">
-        <v>142500</v>
+        <v>142800</v>
       </c>
       <c r="J66" s="3">
-        <v>77400</v>
+        <v>77600</v>
       </c>
       <c r="K66" s="3">
         <v>59500</v>
@@ -3139,25 +3139,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-236300</v>
+        <v>-236900</v>
       </c>
       <c r="E72" s="3">
-        <v>-232800</v>
+        <v>-233400</v>
       </c>
       <c r="F72" s="3">
-        <v>-229100</v>
+        <v>-229700</v>
       </c>
       <c r="G72" s="3">
-        <v>-208900</v>
+        <v>-209400</v>
       </c>
       <c r="H72" s="3">
-        <v>-198700</v>
+        <v>-199200</v>
       </c>
       <c r="I72" s="3">
-        <v>-182500</v>
+        <v>-182900</v>
       </c>
       <c r="J72" s="3">
-        <v>-135600</v>
+        <v>-135900</v>
       </c>
       <c r="K72" s="3">
         <v>-70700</v>
@@ -3313,19 +3313,19 @@
         <v>10700</v>
       </c>
       <c r="F76" s="3">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="G76" s="3">
-        <v>17900</v>
+        <v>18000</v>
       </c>
       <c r="H76" s="3">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="I76" s="3">
         <v>-2700</v>
       </c>
       <c r="J76" s="3">
-        <v>37700</v>
+        <v>37800</v>
       </c>
       <c r="K76" s="3">
         <v>5200</v>
@@ -3441,22 +3441,22 @@
         <v>-3500</v>
       </c>
       <c r="E81" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="F81" s="3">
         <v>-14200</v>
       </c>
       <c r="G81" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="H81" s="3">
         <v>-13800</v>
       </c>
       <c r="I81" s="3">
-        <v>-48000</v>
+        <v>-48200</v>
       </c>
       <c r="J81" s="3">
-        <v>-71000</v>
+        <v>-71200</v>
       </c>
       <c r="K81" s="3">
         <v>-14700</v>
@@ -3750,7 +3750,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-23600</v>
+        <v>-23700</v>
       </c>
       <c r="E89" s="3">
         <v>-11700</v>
@@ -3762,13 +3762,13 @@
         <v>-6600</v>
       </c>
       <c r="H89" s="3">
-        <v>-42600</v>
+        <v>-42700</v>
       </c>
       <c r="I89" s="3">
         <v>-10600</v>
       </c>
       <c r="J89" s="3">
-        <v>-19100</v>
+        <v>-19200</v>
       </c>
       <c r="K89" s="3">
         <v>-5600</v>
@@ -3954,7 +3954,7 @@
         <v>14700</v>
       </c>
       <c r="J94" s="3">
-        <v>-28600</v>
+        <v>-28700</v>
       </c>
       <c r="K94" s="3">
         <v>-5700</v>
@@ -4170,19 +4170,19 @@
         <v>1600</v>
       </c>
       <c r="F100" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="G100" s="3">
         <v>-4000</v>
       </c>
       <c r="H100" s="3">
-        <v>34900</v>
+        <v>35000</v>
       </c>
       <c r="I100" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="J100" s="3">
-        <v>61800</v>
+        <v>61900</v>
       </c>
       <c r="K100" s="3">
         <v>13800</v>
@@ -4257,16 +4257,16 @@
         <v>12800</v>
       </c>
       <c r="G102" s="3">
-        <v>-8600</v>
+        <v>-8700</v>
       </c>
       <c r="H102" s="3">
-        <v>-13200</v>
+        <v>-13300</v>
       </c>
       <c r="I102" s="3">
         <v>11200</v>
       </c>
       <c r="J102" s="3">
-        <v>13700</v>
+        <v>13800</v>
       </c>
       <c r="K102" s="3">
         <v>2000</v>

--- a/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>YTRA</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41730</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>46200</v>
+        <v>50800</v>
       </c>
       <c r="E8" s="3">
-        <v>24000</v>
+        <v>45900</v>
       </c>
       <c r="F8" s="3">
-        <v>15300</v>
+        <v>23900</v>
       </c>
       <c r="G8" s="3">
-        <v>87500</v>
+        <v>15200</v>
       </c>
       <c r="H8" s="3">
-        <v>112900</v>
+        <v>87000</v>
       </c>
       <c r="I8" s="3">
-        <v>147700</v>
+        <v>112200</v>
       </c>
       <c r="J8" s="3">
+        <v>146900</v>
+      </c>
+      <c r="K8" s="3">
         <v>112800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>84300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>8100</v>
+        <v>10500</v>
       </c>
       <c r="E9" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
-        <v>35300</v>
-      </c>
       <c r="H9" s="3">
-        <v>51700</v>
+        <v>35000</v>
       </c>
       <c r="I9" s="3">
-        <v>59500</v>
+        <v>51400</v>
       </c>
       <c r="J9" s="3">
+        <v>59100</v>
+      </c>
+      <c r="K9" s="3">
         <v>50400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>50300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>38100</v>
+        <v>40300</v>
       </c>
       <c r="E10" s="3">
-        <v>22100</v>
+        <v>37900</v>
       </c>
       <c r="F10" s="3">
-        <v>15100</v>
+        <v>21900</v>
       </c>
       <c r="G10" s="3">
-        <v>52300</v>
+        <v>15000</v>
       </c>
       <c r="H10" s="3">
-        <v>61200</v>
+        <v>52000</v>
       </c>
       <c r="I10" s="3">
-        <v>88300</v>
+        <v>60900</v>
       </c>
       <c r="J10" s="3">
+        <v>87700</v>
+      </c>
+      <c r="K10" s="3">
         <v>62400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,38 +962,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
-        <v>1600</v>
-      </c>
       <c r="F14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G14" s="3">
         <v>3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2700</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>51200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -988,51 +1007,57 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>45500</v>
+        <v>52900</v>
       </c>
       <c r="E17" s="3">
-        <v>29900</v>
+        <v>45200</v>
       </c>
       <c r="F17" s="3">
-        <v>33100</v>
+        <v>29700</v>
       </c>
       <c r="G17" s="3">
-        <v>95100</v>
+        <v>32900</v>
       </c>
       <c r="H17" s="3">
-        <v>144000</v>
+        <v>94500</v>
       </c>
       <c r="I17" s="3">
-        <v>188200</v>
+        <v>143100</v>
       </c>
       <c r="J17" s="3">
+        <v>187100</v>
+      </c>
+      <c r="K17" s="3">
         <v>186500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>115500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>97100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5900</v>
-      </c>
       <c r="F18" s="3">
-        <v>-17700</v>
+        <v>-5800</v>
       </c>
       <c r="G18" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="H18" s="3">
         <v>-7500</v>
       </c>
-      <c r="H18" s="3">
-        <v>-31100</v>
-      </c>
       <c r="I18" s="3">
-        <v>-40500</v>
+        <v>-30900</v>
       </c>
       <c r="J18" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-73600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>19000</v>
-      </c>
       <c r="I20" s="3">
-        <v>-6200</v>
+        <v>18900</v>
       </c>
       <c r="J20" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-41600</v>
-      </c>
       <c r="J21" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-66800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-9300</v>
-      </c>
       <c r="H23" s="3">
-        <v>-13800</v>
+        <v>-9200</v>
       </c>
       <c r="I23" s="3">
-        <v>-48200</v>
+        <v>-13700</v>
       </c>
       <c r="J23" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-71100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12800</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>800</v>
       </c>
       <c r="G24" s="3">
         <v>800</v>
       </c>
       <c r="H24" s="3">
+        <v>800</v>
+      </c>
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-14400</v>
-      </c>
       <c r="G26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-10100</v>
       </c>
-      <c r="H26" s="3">
-        <v>-14400</v>
-      </c>
       <c r="I26" s="3">
-        <v>-48900</v>
+        <v>-14300</v>
       </c>
       <c r="J26" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-71600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
-        <v>-5800</v>
-      </c>
       <c r="F27" s="3">
-        <v>-14200</v>
+        <v>-5700</v>
       </c>
       <c r="G27" s="3">
-        <v>-10100</v>
+        <v>-14100</v>
       </c>
       <c r="H27" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-13800</v>
       </c>
-      <c r="I27" s="3">
-        <v>-48200</v>
-      </c>
       <c r="J27" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-71200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>-19000</v>
-      </c>
       <c r="I32" s="3">
-        <v>6200</v>
+        <v>-18900</v>
       </c>
       <c r="J32" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
-        <v>-5800</v>
-      </c>
       <c r="F33" s="3">
-        <v>-14200</v>
+        <v>-5700</v>
       </c>
       <c r="G33" s="3">
-        <v>-10100</v>
+        <v>-14100</v>
       </c>
       <c r="H33" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-13800</v>
       </c>
-      <c r="I33" s="3">
-        <v>-48200</v>
-      </c>
       <c r="J33" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-71200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
-        <v>-5800</v>
-      </c>
       <c r="F35" s="3">
-        <v>-14200</v>
+        <v>-5700</v>
       </c>
       <c r="G35" s="3">
-        <v>-10100</v>
+        <v>-14100</v>
       </c>
       <c r="H35" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-13800</v>
       </c>
-      <c r="I35" s="3">
-        <v>-48200</v>
-      </c>
       <c r="J35" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-71200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41730</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,134 +1988,144 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6100</v>
+        <v>20900</v>
       </c>
       <c r="E41" s="3">
-        <v>9700</v>
+        <v>6000</v>
       </c>
       <c r="F41" s="3">
-        <v>20600</v>
+        <v>9600</v>
       </c>
       <c r="G41" s="3">
-        <v>16500</v>
+        <v>20500</v>
       </c>
       <c r="H41" s="3">
-        <v>26100</v>
+        <v>16400</v>
       </c>
       <c r="I41" s="3">
-        <v>29700</v>
+        <v>25900</v>
       </c>
       <c r="J41" s="3">
+        <v>29600</v>
+      </c>
+      <c r="K41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7800</v>
+        <v>33000</v>
       </c>
       <c r="E42" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G42" s="3">
         <v>7700</v>
       </c>
-      <c r="F42" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G42" s="3">
-        <v>12400</v>
-      </c>
       <c r="H42" s="3">
-        <v>14900</v>
+        <v>12300</v>
       </c>
       <c r="I42" s="3">
-        <v>12700</v>
+        <v>14800</v>
       </c>
       <c r="J42" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K42" s="3">
         <v>36900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>41200</v>
+        <v>59800</v>
       </c>
       <c r="E43" s="3">
-        <v>26300</v>
+        <v>41000</v>
       </c>
       <c r="F43" s="3">
+        <v>26200</v>
+      </c>
+      <c r="G43" s="3">
         <v>14100</v>
       </c>
-      <c r="G43" s="3">
-        <v>35000</v>
-      </c>
       <c r="H43" s="3">
-        <v>65900</v>
+        <v>34800</v>
       </c>
       <c r="I43" s="3">
-        <v>52800</v>
+        <v>65600</v>
       </c>
       <c r="J43" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K43" s="3">
         <v>27600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2050,239 +2145,257 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
-      </c>
-      <c r="K44" s="3">
-        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
       </c>
       <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10900</v>
+        <v>17300</v>
       </c>
       <c r="E45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="F45" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9700</v>
-      </c>
       <c r="H45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I45" s="3">
         <v>10200</v>
       </c>
-      <c r="I45" s="3">
-        <v>11300</v>
-      </c>
       <c r="J45" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K45" s="3">
         <v>8700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>66000</v>
+        <v>130900</v>
       </c>
       <c r="E46" s="3">
-        <v>50500</v>
+        <v>65700</v>
       </c>
       <c r="F46" s="3">
-        <v>49400</v>
+        <v>50200</v>
       </c>
       <c r="G46" s="3">
-        <v>73600</v>
+        <v>49100</v>
       </c>
       <c r="H46" s="3">
-        <v>117200</v>
+        <v>73200</v>
       </c>
       <c r="I46" s="3">
-        <v>106700</v>
+        <v>116500</v>
       </c>
       <c r="J46" s="3">
+        <v>106100</v>
+      </c>
+      <c r="K46" s="3">
         <v>91900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48200</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>700</v>
+        <v>1900</v>
       </c>
       <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>500</v>
+      </c>
+      <c r="H47" s="3">
+        <v>400</v>
+      </c>
+      <c r="I47" s="3">
         <v>600</v>
       </c>
-      <c r="F47" s="3">
-        <v>500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>700</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="E48" s="3">
         <v>3000</v>
       </c>
       <c r="F48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G48" s="3">
         <v>5700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9400</v>
+        <v>11000</v>
       </c>
       <c r="E49" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F49" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G49" s="3">
         <v>10700</v>
       </c>
-      <c r="G49" s="3">
-        <v>20500</v>
-      </c>
       <c r="H49" s="3">
-        <v>27000</v>
+        <v>20400</v>
       </c>
       <c r="I49" s="3">
         <v>26800</v>
       </c>
       <c r="J49" s="3">
+        <v>26700</v>
+      </c>
+      <c r="K49" s="3">
         <v>19400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
-        <v>2700</v>
+        <v>3100</v>
       </c>
       <c r="F52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
-        <v>3900</v>
-      </c>
       <c r="H52" s="3">
-        <v>4700</v>
+        <v>3800</v>
       </c>
       <c r="I52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J52" s="3">
         <v>2800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>81600</v>
+        <v>149300</v>
       </c>
       <c r="E54" s="3">
-        <v>65900</v>
+        <v>81100</v>
       </c>
       <c r="F54" s="3">
-        <v>69300</v>
+        <v>65500</v>
       </c>
       <c r="G54" s="3">
-        <v>105600</v>
+        <v>68900</v>
       </c>
       <c r="H54" s="3">
-        <v>151400</v>
+        <v>105000</v>
       </c>
       <c r="I54" s="3">
-        <v>140100</v>
+        <v>150500</v>
       </c>
       <c r="J54" s="3">
+        <v>139300</v>
+      </c>
+      <c r="K54" s="3">
         <v>115500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>60500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69500</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>26200</v>
+        <v>30900</v>
       </c>
       <c r="E57" s="3">
-        <v>28900</v>
+        <v>26100</v>
       </c>
       <c r="F57" s="3">
-        <v>26700</v>
+        <v>28700</v>
       </c>
       <c r="G57" s="3">
-        <v>34500</v>
+        <v>26600</v>
       </c>
       <c r="H57" s="3">
-        <v>63500</v>
+        <v>34300</v>
       </c>
       <c r="I57" s="3">
-        <v>60900</v>
+        <v>63100</v>
       </c>
       <c r="J57" s="3">
+        <v>60500</v>
+      </c>
+      <c r="K57" s="3">
         <v>38000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>28700</v>
+        <v>6900</v>
       </c>
       <c r="E58" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F58" s="3">
         <v>4700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12500</v>
       </c>
-      <c r="H58" s="3">
-        <v>13900</v>
-      </c>
       <c r="I58" s="3">
+        <v>13800</v>
+      </c>
+      <c r="J58" s="3">
         <v>5900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14700</v>
+        <v>13900</v>
       </c>
       <c r="E59" s="3">
-        <v>16800</v>
+        <v>14600</v>
       </c>
       <c r="F59" s="3">
-        <v>12700</v>
+        <v>16700</v>
       </c>
       <c r="G59" s="3">
-        <v>30300</v>
+        <v>12600</v>
       </c>
       <c r="H59" s="3">
-        <v>42300</v>
+        <v>30100</v>
       </c>
       <c r="I59" s="3">
-        <v>62900</v>
+        <v>42000</v>
       </c>
       <c r="J59" s="3">
+        <v>62600</v>
+      </c>
+      <c r="K59" s="3">
         <v>32200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>69600</v>
+        <v>51700</v>
       </c>
       <c r="E60" s="3">
-        <v>50500</v>
+        <v>69200</v>
       </c>
       <c r="F60" s="3">
-        <v>41800</v>
+        <v>50200</v>
       </c>
       <c r="G60" s="3">
-        <v>77300</v>
+        <v>41600</v>
       </c>
       <c r="H60" s="3">
-        <v>119700</v>
+        <v>76800</v>
       </c>
       <c r="I60" s="3">
-        <v>129800</v>
+        <v>119000</v>
       </c>
       <c r="J60" s="3">
+        <v>129000</v>
+      </c>
+      <c r="K60" s="3">
         <v>70300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>42200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5200</v>
       </c>
-      <c r="G61" s="3">
-        <v>5900</v>
-      </c>
       <c r="H61" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8200</v>
       </c>
-      <c r="G62" s="3">
-        <v>4300</v>
-      </c>
       <c r="H62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>73100</v>
+        <v>82600</v>
       </c>
       <c r="E66" s="3">
-        <v>55200</v>
+        <v>72600</v>
       </c>
       <c r="F66" s="3">
-        <v>55300</v>
+        <v>54800</v>
       </c>
       <c r="G66" s="3">
-        <v>87600</v>
+        <v>55000</v>
       </c>
       <c r="H66" s="3">
-        <v>122900</v>
+        <v>87100</v>
       </c>
       <c r="I66" s="3">
-        <v>142800</v>
+        <v>122200</v>
       </c>
       <c r="J66" s="3">
+        <v>142000</v>
+      </c>
+      <c r="K66" s="3">
         <v>77600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-236900</v>
+        <v>-176100</v>
       </c>
       <c r="E72" s="3">
-        <v>-233400</v>
+        <v>-235500</v>
       </c>
       <c r="F72" s="3">
-        <v>-229700</v>
+        <v>-232000</v>
       </c>
       <c r="G72" s="3">
-        <v>-209400</v>
+        <v>-228400</v>
       </c>
       <c r="H72" s="3">
-        <v>-199200</v>
+        <v>-208200</v>
       </c>
       <c r="I72" s="3">
-        <v>-182900</v>
+        <v>-198100</v>
       </c>
       <c r="J72" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-135900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-70700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-61300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-54500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E76" s="3">
         <v>8500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10700</v>
       </c>
-      <c r="F76" s="3">
-        <v>14000</v>
-      </c>
       <c r="G76" s="3">
-        <v>18000</v>
+        <v>13900</v>
       </c>
       <c r="H76" s="3">
-        <v>28500</v>
+        <v>17900</v>
       </c>
       <c r="I76" s="3">
+        <v>28300</v>
+      </c>
+      <c r="J76" s="3">
         <v>-2700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41730</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
-        <v>-5800</v>
-      </c>
       <c r="F81" s="3">
-        <v>-14200</v>
+        <v>-5700</v>
       </c>
       <c r="G81" s="3">
-        <v>-10100</v>
+        <v>-14100</v>
       </c>
       <c r="H81" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-13800</v>
       </c>
-      <c r="I81" s="3">
-        <v>-48200</v>
-      </c>
       <c r="J81" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-71200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>2300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-23700</v>
+        <v>-17100</v>
       </c>
       <c r="E89" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6600</v>
       </c>
-      <c r="H89" s="3">
-        <v>-42700</v>
-      </c>
       <c r="I89" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="J89" s="3">
         <v>-10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4900</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-800</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
       </c>
       <c r="L91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1800</v>
+        <v>-27500</v>
       </c>
       <c r="E94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7800</v>
       </c>
-      <c r="I94" s="3">
-        <v>14700</v>
-      </c>
       <c r="J94" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-28700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>21100</v>
+        <v>59800</v>
       </c>
       <c r="E100" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
-        <v>6500</v>
-      </c>
       <c r="G100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
-        <v>35000</v>
-      </c>
       <c r="I100" s="3">
-        <v>7000</v>
+        <v>34800</v>
       </c>
       <c r="J100" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K100" s="3">
         <v>61900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3600</v>
       </c>
-      <c r="E102" s="3">
-        <v>-11000</v>
-      </c>
       <c r="F102" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="G102" s="3">
         <v>12800</v>
       </c>
-      <c r="G102" s="3">
-        <v>-8700</v>
-      </c>
       <c r="H102" s="3">
-        <v>-13300</v>
+        <v>-8600</v>
       </c>
       <c r="I102" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="J102" s="3">
         <v>11200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>YTRA</t>
   </si>
@@ -728,25 +728,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>50800</v>
+        <v>49900</v>
       </c>
       <c r="E8" s="3">
-        <v>45900</v>
+        <v>45600</v>
       </c>
       <c r="F8" s="3">
-        <v>23900</v>
+        <v>23700</v>
       </c>
       <c r="G8" s="3">
         <v>15200</v>
       </c>
       <c r="H8" s="3">
-        <v>87000</v>
+        <v>86500</v>
       </c>
       <c r="I8" s="3">
-        <v>112200</v>
+        <v>111600</v>
       </c>
       <c r="J8" s="3">
-        <v>146900</v>
+        <v>146000</v>
       </c>
       <c r="K8" s="3">
         <v>112800</v>
@@ -773,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10500</v>
+        <v>10300</v>
       </c>
       <c r="E9" s="3">
         <v>8000</v>
@@ -785,13 +785,13 @@
         <v>300</v>
       </c>
       <c r="H9" s="3">
-        <v>35000</v>
+        <v>34800</v>
       </c>
       <c r="I9" s="3">
-        <v>51400</v>
+        <v>51100</v>
       </c>
       <c r="J9" s="3">
-        <v>59100</v>
+        <v>58800</v>
       </c>
       <c r="K9" s="3">
         <v>50400</v>
@@ -818,25 +818,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>40300</v>
+        <v>39600</v>
       </c>
       <c r="E10" s="3">
-        <v>37900</v>
+        <v>37600</v>
       </c>
       <c r="F10" s="3">
-        <v>21900</v>
+        <v>21800</v>
       </c>
       <c r="G10" s="3">
-        <v>15000</v>
+        <v>14900</v>
       </c>
       <c r="H10" s="3">
-        <v>52000</v>
+        <v>51700</v>
       </c>
       <c r="I10" s="3">
-        <v>60900</v>
+        <v>60500</v>
       </c>
       <c r="J10" s="3">
-        <v>87700</v>
+        <v>87200</v>
       </c>
       <c r="K10" s="3">
         <v>62400</v>
@@ -972,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
         <v>300</v>
@@ -984,7 +984,7 @@
         <v>3200</v>
       </c>
       <c r="H14" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1026,13 +1026,13 @@
         <v>3700</v>
       </c>
       <c r="G15" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="H15" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="I15" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="J15" s="3">
         <v>5100</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>52900</v>
+        <v>52500</v>
       </c>
       <c r="E17" s="3">
-        <v>45200</v>
+        <v>45000</v>
       </c>
       <c r="F17" s="3">
-        <v>29700</v>
+        <v>29500</v>
       </c>
       <c r="G17" s="3">
-        <v>32900</v>
+        <v>32700</v>
       </c>
       <c r="H17" s="3">
-        <v>94500</v>
+        <v>94000</v>
       </c>
       <c r="I17" s="3">
-        <v>143100</v>
+        <v>142300</v>
       </c>
       <c r="J17" s="3">
-        <v>187100</v>
+        <v>186100</v>
       </c>
       <c r="K17" s="3">
         <v>186500</v>
@@ -1123,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2100</v>
+        <v>-2500</v>
       </c>
       <c r="E18" s="3">
         <v>700</v>
@@ -1132,16 +1132,16 @@
         <v>-5800</v>
       </c>
       <c r="G18" s="3">
-        <v>-17600</v>
+        <v>-17500</v>
       </c>
       <c r="H18" s="3">
         <v>-7500</v>
       </c>
       <c r="I18" s="3">
-        <v>-30900</v>
+        <v>-30700</v>
       </c>
       <c r="J18" s="3">
-        <v>-40300</v>
+        <v>-40100</v>
       </c>
       <c r="K18" s="3">
         <v>-73600</v>
@@ -1187,7 +1187,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1400</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="3">
         <v>-1600</v>
@@ -1196,13 +1196,13 @@
         <v>900</v>
       </c>
       <c r="G20" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="J20" s="3">
         <v>-6100</v>
@@ -1231,8 +1231,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>1300</v>
       </c>
       <c r="E21" s="3">
         <v>1400</v>
@@ -1250,7 +1250,7 @@
         <v>-5000</v>
       </c>
       <c r="J21" s="3">
-        <v>-41300</v>
+        <v>-41100</v>
       </c>
       <c r="K21" s="3">
         <v>-66800</v>
@@ -1276,8 +1276,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>2900</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
@@ -1289,10 +1289,10 @@
         <v>1100</v>
       </c>
       <c r="H22" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="I22" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="J22" s="3">
         <v>1500</v>
@@ -1322,16 +1322,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3500</v>
+        <v>-3900</v>
       </c>
       <c r="E23" s="3">
         <v>-2900</v>
       </c>
       <c r="F23" s="3">
-        <v>-5600</v>
+        <v>-5500</v>
       </c>
       <c r="G23" s="3">
-        <v>-13600</v>
+        <v>-13500</v>
       </c>
       <c r="H23" s="3">
         <v>-9200</v>
@@ -1340,7 +1340,7 @@
         <v>-13700</v>
       </c>
       <c r="J23" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="K23" s="3">
         <v>-71100</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3900</v>
+        <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="F26" s="3">
         <v>-5800</v>
       </c>
       <c r="G26" s="3">
-        <v>-14300</v>
+        <v>-14200</v>
       </c>
       <c r="H26" s="3">
-        <v>-10100</v>
+        <v>-10000</v>
       </c>
       <c r="I26" s="3">
-        <v>-14300</v>
+        <v>-14200</v>
       </c>
       <c r="J26" s="3">
-        <v>-48600</v>
+        <v>-48300</v>
       </c>
       <c r="K26" s="3">
         <v>-71600</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3800</v>
+        <v>-4200</v>
       </c>
       <c r="E27" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="F27" s="3">
         <v>-5700</v>
       </c>
       <c r="G27" s="3">
-        <v>-14100</v>
+        <v>-14000</v>
       </c>
       <c r="H27" s="3">
-        <v>-10000</v>
+        <v>-9900</v>
       </c>
       <c r="I27" s="3">
-        <v>-13800</v>
+        <v>-13700</v>
       </c>
       <c r="J27" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="K27" s="3">
         <v>-71200</v>
@@ -1727,7 +1727,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1400</v>
+        <v>-1500</v>
       </c>
       <c r="E32" s="3">
         <v>1600</v>
@@ -1736,13 +1736,13 @@
         <v>-900</v>
       </c>
       <c r="G32" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-18900</v>
+        <v>-18800</v>
       </c>
       <c r="J32" s="3">
         <v>6100</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3800</v>
+        <v>-4200</v>
       </c>
       <c r="E33" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="F33" s="3">
         <v>-5700</v>
       </c>
       <c r="G33" s="3">
-        <v>-14100</v>
+        <v>-14000</v>
       </c>
       <c r="H33" s="3">
-        <v>-10000</v>
+        <v>-9900</v>
       </c>
       <c r="I33" s="3">
-        <v>-13800</v>
+        <v>-13700</v>
       </c>
       <c r="J33" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="K33" s="3">
         <v>-71200</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3800</v>
+        <v>-4200</v>
       </c>
       <c r="E35" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="F35" s="3">
         <v>-5700</v>
       </c>
       <c r="G35" s="3">
-        <v>-14100</v>
+        <v>-14000</v>
       </c>
       <c r="H35" s="3">
-        <v>-10000</v>
+        <v>-9900</v>
       </c>
       <c r="I35" s="3">
-        <v>-13800</v>
+        <v>-13700</v>
       </c>
       <c r="J35" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="K35" s="3">
         <v>-71200</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>20900</v>
+        <v>20800</v>
       </c>
       <c r="E41" s="3">
         <v>6000</v>
       </c>
       <c r="F41" s="3">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="G41" s="3">
-        <v>20500</v>
+        <v>20400</v>
       </c>
       <c r="H41" s="3">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="I41" s="3">
-        <v>25900</v>
+        <v>25800</v>
       </c>
       <c r="J41" s="3">
-        <v>29600</v>
+        <v>29400</v>
       </c>
       <c r="K41" s="3">
         <v>18500</v>
@@ -2040,10 +2040,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33000</v>
+        <v>31200</v>
       </c>
       <c r="E42" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="F42" s="3">
         <v>6800</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>59800</v>
+        <v>61000</v>
       </c>
       <c r="E43" s="3">
-        <v>41000</v>
+        <v>40700</v>
       </c>
       <c r="F43" s="3">
-        <v>26200</v>
+        <v>26000</v>
       </c>
       <c r="G43" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="3">
-        <v>34800</v>
+        <v>34600</v>
       </c>
       <c r="I43" s="3">
-        <v>65600</v>
+        <v>65200</v>
       </c>
       <c r="J43" s="3">
-        <v>52500</v>
+        <v>52100</v>
       </c>
       <c r="K43" s="3">
         <v>27600</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17300</v>
+        <v>17700</v>
       </c>
       <c r="E45" s="3">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="F45" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="G45" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="H45" s="3">
         <v>9600</v>
       </c>
       <c r="I45" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="J45" s="3">
-        <v>11200</v>
+        <v>11100</v>
       </c>
       <c r="K45" s="3">
         <v>8700</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>130900</v>
+        <v>130700</v>
       </c>
       <c r="E46" s="3">
-        <v>65700</v>
+        <v>65300</v>
       </c>
       <c r="F46" s="3">
-        <v>50200</v>
+        <v>49900</v>
       </c>
       <c r="G46" s="3">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="H46" s="3">
-        <v>73200</v>
+        <v>72700</v>
       </c>
       <c r="I46" s="3">
-        <v>116500</v>
+        <v>115900</v>
       </c>
       <c r="J46" s="3">
-        <v>106100</v>
+        <v>105500</v>
       </c>
       <c r="K46" s="3">
         <v>91900</v>
@@ -2265,7 +2265,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -2313,7 +2313,7 @@
         <v>2800</v>
       </c>
       <c r="E48" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="F48" s="3">
         <v>3000</v>
@@ -2355,7 +2355,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="E49" s="3">
         <v>9300</v>
@@ -2364,16 +2364,16 @@
         <v>9000</v>
       </c>
       <c r="G49" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="H49" s="3">
-        <v>20400</v>
+        <v>20300</v>
       </c>
       <c r="I49" s="3">
-        <v>26800</v>
+        <v>26700</v>
       </c>
       <c r="J49" s="3">
-        <v>26700</v>
+        <v>26500</v>
       </c>
       <c r="K49" s="3">
         <v>19400</v>
@@ -2490,7 +2490,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="E52" s="3">
         <v>3100</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>149300</v>
+        <v>148900</v>
       </c>
       <c r="E54" s="3">
-        <v>81100</v>
+        <v>80600</v>
       </c>
       <c r="F54" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="G54" s="3">
-        <v>68900</v>
+        <v>68500</v>
       </c>
       <c r="H54" s="3">
-        <v>105000</v>
+        <v>104400</v>
       </c>
       <c r="I54" s="3">
-        <v>150500</v>
+        <v>149600</v>
       </c>
       <c r="J54" s="3">
-        <v>139300</v>
+        <v>138500</v>
       </c>
       <c r="K54" s="3">
         <v>115500</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>30900</v>
+        <v>31100</v>
       </c>
       <c r="E57" s="3">
-        <v>26100</v>
+        <v>25900</v>
       </c>
       <c r="F57" s="3">
-        <v>28700</v>
+        <v>28500</v>
       </c>
       <c r="G57" s="3">
-        <v>26600</v>
+        <v>26400</v>
       </c>
       <c r="H57" s="3">
-        <v>34300</v>
+        <v>34100</v>
       </c>
       <c r="I57" s="3">
-        <v>63100</v>
+        <v>62800</v>
       </c>
       <c r="J57" s="3">
-        <v>60500</v>
+        <v>60200</v>
       </c>
       <c r="K57" s="3">
         <v>38000</v>
@@ -2711,7 +2711,7 @@
         <v>6900</v>
       </c>
       <c r="E58" s="3">
-        <v>28600</v>
+        <v>28400</v>
       </c>
       <c r="F58" s="3">
         <v>4700</v>
@@ -2720,10 +2720,10 @@
         <v>2400</v>
       </c>
       <c r="H58" s="3">
-        <v>12500</v>
+        <v>12400</v>
       </c>
       <c r="I58" s="3">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="J58" s="3">
         <v>5900</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13900</v>
+        <v>14400</v>
       </c>
       <c r="E59" s="3">
-        <v>14600</v>
+        <v>14500</v>
       </c>
       <c r="F59" s="3">
-        <v>16700</v>
+        <v>16600</v>
       </c>
       <c r="G59" s="3">
-        <v>12600</v>
+        <v>12500</v>
       </c>
       <c r="H59" s="3">
-        <v>30100</v>
+        <v>29900</v>
       </c>
       <c r="I59" s="3">
-        <v>42000</v>
+        <v>41800</v>
       </c>
       <c r="J59" s="3">
-        <v>62600</v>
+        <v>62200</v>
       </c>
       <c r="K59" s="3">
         <v>32200</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>51700</v>
+        <v>52300</v>
       </c>
       <c r="E60" s="3">
-        <v>69200</v>
+        <v>68800</v>
       </c>
       <c r="F60" s="3">
-        <v>50200</v>
+        <v>49900</v>
       </c>
       <c r="G60" s="3">
-        <v>41600</v>
+        <v>41400</v>
       </c>
       <c r="H60" s="3">
-        <v>76800</v>
+        <v>76400</v>
       </c>
       <c r="I60" s="3">
-        <v>119000</v>
+        <v>118300</v>
       </c>
       <c r="J60" s="3">
-        <v>129000</v>
+        <v>128200</v>
       </c>
       <c r="K60" s="3">
         <v>70300</v>
@@ -2852,7 +2852,7 @@
         <v>2800</v>
       </c>
       <c r="G61" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="H61" s="3">
         <v>5800</v>
@@ -2897,7 +2897,7 @@
         <v>1800</v>
       </c>
       <c r="G62" s="3">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="H62" s="3">
         <v>4200</v>
@@ -2906,7 +2906,7 @@
         <v>2700</v>
       </c>
       <c r="J62" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="K62" s="3">
         <v>6300</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>82600</v>
+        <v>144600</v>
       </c>
       <c r="E66" s="3">
-        <v>72600</v>
+        <v>72200</v>
       </c>
       <c r="F66" s="3">
-        <v>54800</v>
+        <v>54500</v>
       </c>
       <c r="G66" s="3">
-        <v>55000</v>
+        <v>54700</v>
       </c>
       <c r="H66" s="3">
-        <v>87100</v>
+        <v>86600</v>
       </c>
       <c r="I66" s="3">
-        <v>122200</v>
+        <v>121500</v>
       </c>
       <c r="J66" s="3">
-        <v>142000</v>
+        <v>141200</v>
       </c>
       <c r="K66" s="3">
         <v>77600</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-176100</v>
+        <v>-237100</v>
       </c>
       <c r="E72" s="3">
-        <v>-235500</v>
+        <v>-234100</v>
       </c>
       <c r="F72" s="3">
-        <v>-232000</v>
+        <v>-230700</v>
       </c>
       <c r="G72" s="3">
-        <v>-228400</v>
+        <v>-227000</v>
       </c>
       <c r="H72" s="3">
-        <v>-208200</v>
+        <v>-207000</v>
       </c>
       <c r="I72" s="3">
-        <v>-198100</v>
+        <v>-196900</v>
       </c>
       <c r="J72" s="3">
-        <v>-181900</v>
+        <v>-180800</v>
       </c>
       <c r="K72" s="3">
         <v>-135900</v>
@@ -3492,22 +3492,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>66600</v>
+        <v>4200</v>
       </c>
       <c r="E76" s="3">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="F76" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="G76" s="3">
-        <v>13900</v>
+        <v>13800</v>
       </c>
       <c r="H76" s="3">
-        <v>17900</v>
+        <v>17800</v>
       </c>
       <c r="I76" s="3">
-        <v>28300</v>
+        <v>28100</v>
       </c>
       <c r="J76" s="3">
         <v>-2700</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3800</v>
+        <v>-4200</v>
       </c>
       <c r="E81" s="3">
-        <v>-3500</v>
+        <v>-3400</v>
       </c>
       <c r="F81" s="3">
         <v>-5700</v>
       </c>
       <c r="G81" s="3">
-        <v>-14100</v>
+        <v>-14000</v>
       </c>
       <c r="H81" s="3">
-        <v>-10000</v>
+        <v>-9900</v>
       </c>
       <c r="I81" s="3">
-        <v>-13800</v>
+        <v>-13700</v>
       </c>
       <c r="J81" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="K81" s="3">
         <v>-71200</v>
@@ -3695,8 +3695,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>2400</v>
       </c>
       <c r="E83" s="3">
         <v>2300</v>
@@ -3705,13 +3705,13 @@
         <v>3700</v>
       </c>
       <c r="G83" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="H83" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="I83" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="J83" s="3">
         <v>5100</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-17100</v>
+        <v>-17800</v>
       </c>
       <c r="E89" s="3">
-        <v>-23500</v>
+        <v>-23400</v>
       </c>
       <c r="F89" s="3">
-        <v>-11700</v>
+        <v>-11600</v>
       </c>
       <c r="G89" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="H89" s="3">
         <v>-6600</v>
       </c>
       <c r="I89" s="3">
-        <v>-42500</v>
+        <v>-42200</v>
       </c>
       <c r="J89" s="3">
-        <v>-10600</v>
+        <v>-10500</v>
       </c>
       <c r="K89" s="3">
         <v>-19200</v>
@@ -4029,8 +4029,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -4165,7 +4165,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-27500</v>
+        <v>-27400</v>
       </c>
       <c r="E94" s="3">
         <v>-1700</v>
@@ -4174,7 +4174,7 @@
         <v>-1000</v>
       </c>
       <c r="G94" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H94" s="3">
         <v>1200</v>
@@ -4409,10 +4409,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>59800</v>
+        <v>61200</v>
       </c>
       <c r="E100" s="3">
-        <v>21000</v>
+        <v>20900</v>
       </c>
       <c r="F100" s="3">
         <v>1600</v>
@@ -4424,7 +4424,7 @@
         <v>-4000</v>
       </c>
       <c r="I100" s="3">
-        <v>34800</v>
+        <v>34600</v>
       </c>
       <c r="J100" s="3">
         <v>6900</v>
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6000</v>
+        <v>-1300</v>
       </c>
       <c r="E101" s="3">
         <v>700</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>21200</v>
+        <v>14800</v>
       </c>
       <c r="E102" s="3">
-        <v>-3600</v>
+        <v>-3500</v>
       </c>
       <c r="F102" s="3">
         <v>-10900</v>
       </c>
       <c r="G102" s="3">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="H102" s="3">
         <v>-8600</v>
       </c>
       <c r="I102" s="3">
-        <v>-13200</v>
+        <v>-13100</v>
       </c>
       <c r="J102" s="3">
-        <v>11200</v>
+        <v>11100</v>
       </c>
       <c r="K102" s="3">
         <v>13800</v>

--- a/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>YTRA</t>
   </si>
@@ -728,25 +728,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>49900</v>
+        <v>50300</v>
       </c>
       <c r="E8" s="3">
-        <v>45600</v>
+        <v>46600</v>
       </c>
       <c r="F8" s="3">
-        <v>23700</v>
+        <v>26200</v>
       </c>
       <c r="G8" s="3">
-        <v>15200</v>
+        <v>17400</v>
       </c>
       <c r="H8" s="3">
-        <v>86500</v>
+        <v>96400</v>
       </c>
       <c r="I8" s="3">
-        <v>111600</v>
+        <v>135100</v>
       </c>
       <c r="J8" s="3">
-        <v>146000</v>
+        <v>188200</v>
       </c>
       <c r="K8" s="3">
         <v>112800</v>
@@ -773,25 +773,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10300</v>
+        <v>27200</v>
       </c>
       <c r="E9" s="3">
-        <v>8000</v>
+        <v>22700</v>
       </c>
       <c r="F9" s="3">
-        <v>1900</v>
+        <v>16000</v>
       </c>
       <c r="G9" s="3">
-        <v>300</v>
+        <v>11400</v>
       </c>
       <c r="H9" s="3">
-        <v>34800</v>
+        <v>63500</v>
       </c>
       <c r="I9" s="3">
-        <v>51100</v>
+        <v>99900</v>
       </c>
       <c r="J9" s="3">
-        <v>58800</v>
+        <v>121800</v>
       </c>
       <c r="K9" s="3">
         <v>50400</v>
@@ -818,25 +818,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>39600</v>
+        <v>23100</v>
       </c>
       <c r="E10" s="3">
-        <v>37600</v>
+        <v>23900</v>
       </c>
       <c r="F10" s="3">
-        <v>21800</v>
+        <v>10200</v>
       </c>
       <c r="G10" s="3">
-        <v>14900</v>
+        <v>6000</v>
       </c>
       <c r="H10" s="3">
-        <v>51700</v>
+        <v>32900</v>
       </c>
       <c r="I10" s="3">
-        <v>60500</v>
+        <v>35100</v>
       </c>
       <c r="J10" s="3">
-        <v>87200</v>
+        <v>66400</v>
       </c>
       <c r="K10" s="3">
         <v>62400</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>600</v>
+        <v>-600</v>
       </c>
       <c r="E14" s="3">
-        <v>300</v>
+        <v>-1500</v>
       </c>
       <c r="F14" s="3">
-        <v>1500</v>
+        <v>-400</v>
       </c>
       <c r="G14" s="3">
-        <v>3200</v>
+        <v>1900</v>
       </c>
       <c r="H14" s="3">
-        <v>2600</v>
+        <v>-3200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="K14" s="3">
         <v>51200</v>
@@ -1023,19 +1023,19 @@
         <v>2300</v>
       </c>
       <c r="F15" s="3">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="G15" s="3">
-        <v>8900</v>
+        <v>10200</v>
       </c>
       <c r="H15" s="3">
-        <v>7900</v>
+        <v>8800</v>
       </c>
       <c r="I15" s="3">
-        <v>6900</v>
+        <v>8400</v>
       </c>
       <c r="J15" s="3">
-        <v>5100</v>
+        <v>6500</v>
       </c>
       <c r="K15" s="3">
         <v>3300</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>52500</v>
+        <v>53400</v>
       </c>
       <c r="E17" s="3">
-        <v>45000</v>
+        <v>47400</v>
       </c>
       <c r="F17" s="3">
-        <v>29500</v>
+        <v>33000</v>
       </c>
       <c r="G17" s="3">
-        <v>32700</v>
+        <v>35500</v>
       </c>
       <c r="H17" s="3">
-        <v>94000</v>
+        <v>107900</v>
       </c>
       <c r="I17" s="3">
-        <v>142300</v>
+        <v>165700</v>
       </c>
       <c r="J17" s="3">
-        <v>186100</v>
+        <v>235400</v>
       </c>
       <c r="K17" s="3">
         <v>186500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2500</v>
+        <v>-3100</v>
       </c>
       <c r="E18" s="3">
-        <v>700</v>
+        <v>-800</v>
       </c>
       <c r="F18" s="3">
-        <v>-5800</v>
+        <v>-6800</v>
       </c>
       <c r="G18" s="3">
-        <v>-17500</v>
+        <v>-18200</v>
       </c>
       <c r="H18" s="3">
-        <v>-7500</v>
+        <v>-11500</v>
       </c>
       <c r="I18" s="3">
-        <v>-30700</v>
+        <v>-30600</v>
       </c>
       <c r="J18" s="3">
-        <v>-40100</v>
+        <v>-47100</v>
       </c>
       <c r="K18" s="3">
         <v>-73600</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
-        <v>-1600</v>
+        <v>1800</v>
       </c>
       <c r="F20" s="3">
-        <v>900</v>
+        <v>-500</v>
       </c>
       <c r="G20" s="3">
-        <v>5100</v>
+        <v>-4800</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>18800</v>
+        <v>-22300</v>
       </c>
       <c r="J20" s="3">
-        <v>-6100</v>
+        <v>9200</v>
       </c>
       <c r="K20" s="3">
         <v>3500</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1300</v>
+        <v>-1300</v>
       </c>
       <c r="E21" s="3">
-        <v>1400</v>
+        <v>-300</v>
       </c>
       <c r="F21" s="3">
-        <v>-1300</v>
+        <v>-2300</v>
       </c>
       <c r="G21" s="3">
-        <v>-3500</v>
+        <v>-3100</v>
       </c>
       <c r="H21" s="3">
-        <v>700</v>
+        <v>-3000</v>
       </c>
       <c r="I21" s="3">
-        <v>-5000</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3">
-        <v>-41100</v>
+        <v>-49700</v>
       </c>
       <c r="K21" s="3">
         <v>-66800</v>
@@ -1283,19 +1283,19 @@
         <v>2000</v>
       </c>
       <c r="F22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G22" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J22" s="3">
         <v>1900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1500</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="E23" s="3">
         <v>-2900</v>
       </c>
       <c r="F23" s="3">
-        <v>-5500</v>
+        <v>-6100</v>
       </c>
       <c r="G23" s="3">
-        <v>-13500</v>
+        <v>-15500</v>
       </c>
       <c r="H23" s="3">
-        <v>-9200</v>
+        <v>-10200</v>
       </c>
       <c r="I23" s="3">
-        <v>-13700</v>
+        <v>-16500</v>
       </c>
       <c r="J23" s="3">
-        <v>-47600</v>
+        <v>-61400</v>
       </c>
       <c r="K23" s="3">
         <v>-71100</v>
@@ -1376,16 +1376,16 @@
         <v>200</v>
       </c>
       <c r="G24" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H24" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I24" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J24" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="K24" s="3">
         <v>500</v>
@@ -1460,22 +1460,22 @@
         <v>-4400</v>
       </c>
       <c r="E26" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="F26" s="3">
-        <v>-5800</v>
+        <v>-6400</v>
       </c>
       <c r="G26" s="3">
-        <v>-14200</v>
+        <v>-16300</v>
       </c>
       <c r="H26" s="3">
-        <v>-10000</v>
+        <v>-11200</v>
       </c>
       <c r="I26" s="3">
-        <v>-14200</v>
+        <v>-17200</v>
       </c>
       <c r="J26" s="3">
-        <v>-48300</v>
+        <v>-62300</v>
       </c>
       <c r="K26" s="3">
         <v>-71600</v>
@@ -1505,22 +1505,22 @@
         <v>-4200</v>
       </c>
       <c r="E27" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="F27" s="3">
-        <v>-5700</v>
+        <v>-6300</v>
       </c>
       <c r="G27" s="3">
-        <v>-14000</v>
+        <v>-16100</v>
       </c>
       <c r="H27" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="I27" s="3">
-        <v>-13700</v>
+        <v>-16600</v>
       </c>
       <c r="J27" s="3">
-        <v>-47600</v>
+        <v>-61400</v>
       </c>
       <c r="K27" s="3">
         <v>-71200</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
-        <v>1600</v>
+        <v>-1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-900</v>
+        <v>500</v>
       </c>
       <c r="G32" s="3">
-        <v>-5100</v>
+        <v>4800</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>-18800</v>
+        <v>22300</v>
       </c>
       <c r="J32" s="3">
-        <v>6100</v>
+        <v>-9200</v>
       </c>
       <c r="K32" s="3">
         <v>-3500</v>
@@ -1775,22 +1775,22 @@
         <v>-4200</v>
       </c>
       <c r="E33" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="F33" s="3">
-        <v>-5700</v>
+        <v>-6300</v>
       </c>
       <c r="G33" s="3">
-        <v>-14000</v>
+        <v>-16100</v>
       </c>
       <c r="H33" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="I33" s="3">
-        <v>-13700</v>
+        <v>-16600</v>
       </c>
       <c r="J33" s="3">
-        <v>-47600</v>
+        <v>-61400</v>
       </c>
       <c r="K33" s="3">
         <v>-71200</v>
@@ -1865,22 +1865,22 @@
         <v>-4200</v>
       </c>
       <c r="E35" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="F35" s="3">
-        <v>-5700</v>
+        <v>-6300</v>
       </c>
       <c r="G35" s="3">
-        <v>-14000</v>
+        <v>-16100</v>
       </c>
       <c r="H35" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="I35" s="3">
-        <v>-13700</v>
+        <v>-16600</v>
       </c>
       <c r="J35" s="3">
-        <v>-47600</v>
+        <v>-61400</v>
       </c>
       <c r="K35" s="3">
         <v>-71200</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>20800</v>
+        <v>20900</v>
       </c>
       <c r="E41" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="F41" s="3">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="G41" s="3">
-        <v>20400</v>
+        <v>23400</v>
       </c>
       <c r="H41" s="3">
-        <v>16300</v>
+        <v>18100</v>
       </c>
       <c r="I41" s="3">
-        <v>25800</v>
+        <v>31200</v>
       </c>
       <c r="J41" s="3">
-        <v>29400</v>
+        <v>37900</v>
       </c>
       <c r="K41" s="3">
         <v>18500</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>31200</v>
+        <v>31500</v>
       </c>
       <c r="E42" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="F42" s="3">
-        <v>6800</v>
+        <v>1100</v>
       </c>
       <c r="G42" s="3">
-        <v>7700</v>
+        <v>7300</v>
       </c>
       <c r="H42" s="3">
-        <v>12300</v>
+        <v>10000</v>
       </c>
       <c r="I42" s="3">
-        <v>14800</v>
+        <v>14500</v>
       </c>
       <c r="J42" s="3">
-        <v>12600</v>
+        <v>15500</v>
       </c>
       <c r="K42" s="3">
         <v>36900</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>61000</v>
+        <v>60200</v>
       </c>
       <c r="E43" s="3">
-        <v>40700</v>
+        <v>41100</v>
       </c>
       <c r="F43" s="3">
-        <v>26000</v>
+        <v>28300</v>
       </c>
       <c r="G43" s="3">
-        <v>14000</v>
+        <v>16700</v>
       </c>
       <c r="H43" s="3">
-        <v>34600</v>
+        <v>40900</v>
       </c>
       <c r="I43" s="3">
-        <v>65200</v>
+        <v>80500</v>
       </c>
       <c r="J43" s="3">
-        <v>52100</v>
+        <v>66800</v>
       </c>
       <c r="K43" s="3">
         <v>27600</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17700</v>
+        <v>18300</v>
       </c>
       <c r="E45" s="3">
-        <v>11600</v>
+        <v>11100</v>
       </c>
       <c r="F45" s="3">
-        <v>7500</v>
+        <v>13800</v>
       </c>
       <c r="G45" s="3">
-        <v>6700</v>
+        <v>7600</v>
       </c>
       <c r="H45" s="3">
-        <v>9600</v>
+        <v>11100</v>
       </c>
       <c r="I45" s="3">
-        <v>10100</v>
+        <v>12900</v>
       </c>
       <c r="J45" s="3">
-        <v>11100</v>
+        <v>14400</v>
       </c>
       <c r="K45" s="3">
         <v>8700</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>130700</v>
+        <v>131600</v>
       </c>
       <c r="E46" s="3">
-        <v>65300</v>
+        <v>66700</v>
       </c>
       <c r="F46" s="3">
-        <v>49900</v>
+        <v>55100</v>
       </c>
       <c r="G46" s="3">
-        <v>48800</v>
+        <v>56000</v>
       </c>
       <c r="H46" s="3">
-        <v>72700</v>
+        <v>81000</v>
       </c>
       <c r="I46" s="3">
-        <v>115900</v>
+        <v>140300</v>
       </c>
       <c r="J46" s="3">
-        <v>105500</v>
+        <v>136000</v>
       </c>
       <c r="K46" s="3">
         <v>91900</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="J47" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="K47" s="3">
         <v>1000</v>
@@ -2313,22 +2313,22 @@
         <v>2800</v>
       </c>
       <c r="E48" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="F48" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G48" s="3">
-        <v>5700</v>
+        <v>6500</v>
       </c>
       <c r="H48" s="3">
-        <v>7200</v>
+        <v>8000</v>
       </c>
       <c r="I48" s="3">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="J48" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="K48" s="3">
         <v>1700</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="E49" s="3">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="F49" s="3">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="G49" s="3">
-        <v>10600</v>
+        <v>12200</v>
       </c>
       <c r="H49" s="3">
-        <v>20300</v>
+        <v>22600</v>
       </c>
       <c r="I49" s="3">
-        <v>26700</v>
+        <v>32300</v>
       </c>
       <c r="J49" s="3">
-        <v>26500</v>
+        <v>34200</v>
       </c>
       <c r="K49" s="3">
         <v>19400</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J52" s="3">
         <v>2900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2800</v>
       </c>
       <c r="K52" s="3">
         <v>1500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>148900</v>
+        <v>149900</v>
       </c>
       <c r="E54" s="3">
-        <v>80600</v>
+        <v>82400</v>
       </c>
       <c r="F54" s="3">
-        <v>65100</v>
+        <v>72000</v>
       </c>
       <c r="G54" s="3">
-        <v>68500</v>
+        <v>78600</v>
       </c>
       <c r="H54" s="3">
-        <v>104400</v>
+        <v>116300</v>
       </c>
       <c r="I54" s="3">
-        <v>149600</v>
+        <v>181200</v>
       </c>
       <c r="J54" s="3">
-        <v>138500</v>
+        <v>178500</v>
       </c>
       <c r="K54" s="3">
         <v>115500</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>31100</v>
+        <v>13800</v>
       </c>
       <c r="E57" s="3">
-        <v>25900</v>
+        <v>13600</v>
       </c>
       <c r="F57" s="3">
-        <v>28500</v>
+        <v>31600</v>
       </c>
       <c r="G57" s="3">
-        <v>26400</v>
+        <v>30300</v>
       </c>
       <c r="H57" s="3">
-        <v>34100</v>
+        <v>38000</v>
       </c>
       <c r="I57" s="3">
-        <v>62800</v>
+        <v>76000</v>
       </c>
       <c r="J57" s="3">
-        <v>60200</v>
+        <v>61100</v>
       </c>
       <c r="K57" s="3">
         <v>38000</v>
@@ -2711,22 +2711,22 @@
         <v>6900</v>
       </c>
       <c r="E58" s="3">
-        <v>28400</v>
+        <v>29000</v>
       </c>
       <c r="F58" s="3">
-        <v>4700</v>
+        <v>5200</v>
       </c>
       <c r="G58" s="3">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="H58" s="3">
-        <v>12400</v>
+        <v>13800</v>
       </c>
       <c r="I58" s="3">
-        <v>13700</v>
+        <v>16600</v>
       </c>
       <c r="J58" s="3">
-        <v>5900</v>
+        <v>7600</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14400</v>
+        <v>24100</v>
       </c>
       <c r="E59" s="3">
-        <v>14500</v>
+        <v>21900</v>
       </c>
       <c r="F59" s="3">
-        <v>16600</v>
+        <v>14900</v>
       </c>
       <c r="G59" s="3">
-        <v>12500</v>
+        <v>11300</v>
       </c>
       <c r="H59" s="3">
-        <v>29900</v>
+        <v>29500</v>
       </c>
       <c r="I59" s="3">
-        <v>41800</v>
+        <v>42700</v>
       </c>
       <c r="J59" s="3">
-        <v>62200</v>
+        <v>82100</v>
       </c>
       <c r="K59" s="3">
         <v>32200</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>52300</v>
+        <v>52700</v>
       </c>
       <c r="E60" s="3">
-        <v>68800</v>
+        <v>70300</v>
       </c>
       <c r="F60" s="3">
-        <v>49900</v>
+        <v>55100</v>
       </c>
       <c r="G60" s="3">
-        <v>41400</v>
+        <v>47400</v>
       </c>
       <c r="H60" s="3">
-        <v>76400</v>
+        <v>85100</v>
       </c>
       <c r="I60" s="3">
-        <v>118300</v>
+        <v>143200</v>
       </c>
       <c r="J60" s="3">
-        <v>128200</v>
+        <v>165300</v>
       </c>
       <c r="K60" s="3">
         <v>70300</v>
@@ -2849,19 +2849,19 @@
         <v>2700</v>
       </c>
       <c r="F61" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="G61" s="3">
-        <v>5100</v>
+        <v>5900</v>
       </c>
       <c r="H61" s="3">
-        <v>5800</v>
+        <v>6400</v>
       </c>
       <c r="I61" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
-        <v>4300</v>
+        <v>5500</v>
       </c>
       <c r="K61" s="3">
         <v>400</v>
@@ -2887,26 +2887,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>700</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
-        <v>1800</v>
-      </c>
       <c r="G62" s="3">
-        <v>8100</v>
+        <v>4800</v>
       </c>
       <c r="H62" s="3">
-        <v>4200</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
-        <v>8600</v>
+        <v>100</v>
       </c>
       <c r="K62" s="3">
         <v>6300</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>144600</v>
+        <v>56800</v>
       </c>
       <c r="E66" s="3">
-        <v>72200</v>
+        <v>73600</v>
       </c>
       <c r="F66" s="3">
-        <v>54500</v>
+        <v>60200</v>
       </c>
       <c r="G66" s="3">
-        <v>54700</v>
+        <v>62700</v>
       </c>
       <c r="H66" s="3">
-        <v>86600</v>
+        <v>96200</v>
       </c>
       <c r="I66" s="3">
-        <v>121500</v>
+        <v>146800</v>
       </c>
       <c r="J66" s="3">
-        <v>141200</v>
+        <v>182000</v>
       </c>
       <c r="K66" s="3">
         <v>77600</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-237100</v>
+        <v>-243200</v>
       </c>
       <c r="E72" s="3">
-        <v>-234100</v>
+        <v>-242600</v>
       </c>
       <c r="F72" s="3">
-        <v>-230700</v>
+        <v>-258500</v>
       </c>
       <c r="G72" s="3">
-        <v>-227000</v>
+        <v>-262000</v>
       </c>
       <c r="H72" s="3">
-        <v>-207000</v>
+        <v>-239800</v>
       </c>
       <c r="I72" s="3">
-        <v>-196900</v>
+        <v>-249100</v>
       </c>
       <c r="J72" s="3">
-        <v>-180800</v>
+        <v>-245900</v>
       </c>
       <c r="K72" s="3">
         <v>-135900</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4200</v>
+        <v>64700</v>
       </c>
       <c r="E76" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="F76" s="3">
-        <v>10600</v>
+        <v>11700</v>
       </c>
       <c r="G76" s="3">
-        <v>13800</v>
+        <v>15800</v>
       </c>
       <c r="H76" s="3">
-        <v>17800</v>
+        <v>19800</v>
       </c>
       <c r="I76" s="3">
-        <v>28100</v>
+        <v>34100</v>
       </c>
       <c r="J76" s="3">
-        <v>-2700</v>
+        <v>-3500</v>
       </c>
       <c r="K76" s="3">
         <v>37800</v>
@@ -3635,22 +3635,22 @@
         <v>-4200</v>
       </c>
       <c r="E81" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="F81" s="3">
-        <v>-5700</v>
+        <v>-6300</v>
       </c>
       <c r="G81" s="3">
-        <v>-14000</v>
+        <v>-16100</v>
       </c>
       <c r="H81" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="I81" s="3">
-        <v>-13700</v>
+        <v>-16600</v>
       </c>
       <c r="J81" s="3">
-        <v>-47600</v>
+        <v>-61400</v>
       </c>
       <c r="K81" s="3">
         <v>-71200</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2400</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>2300</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>8900</v>
+        <v>1700</v>
       </c>
       <c r="H83" s="3">
-        <v>7900</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>6900</v>
+        <v>1800</v>
       </c>
       <c r="J83" s="3">
-        <v>5100</v>
+        <v>1600</v>
       </c>
       <c r="K83" s="3">
         <v>3300</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-17800</v>
+        <v>-17200</v>
       </c>
       <c r="E89" s="3">
-        <v>-23400</v>
+        <v>-23900</v>
       </c>
       <c r="F89" s="3">
-        <v>-11600</v>
+        <v>-12800</v>
       </c>
       <c r="G89" s="3">
-        <v>9100</v>
+        <v>10500</v>
       </c>
       <c r="H89" s="3">
-        <v>-6600</v>
+        <v>-7300</v>
       </c>
       <c r="I89" s="3">
-        <v>-42200</v>
+        <v>-51100</v>
       </c>
       <c r="J89" s="3">
-        <v>-10500</v>
+        <v>-13600</v>
       </c>
       <c r="K89" s="3">
         <v>-19200</v>
@@ -4048,7 +4048,7 @@
         <v>-400</v>
       </c>
       <c r="J91" s="3">
-        <v>-2700</v>
+        <v>-3400</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-27400</v>
+        <v>-27600</v>
       </c>
       <c r="E94" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="F94" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="G94" s="3">
-        <v>-2700</v>
+        <v>-3100</v>
       </c>
       <c r="H94" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I94" s="3">
-        <v>-7800</v>
+        <v>-9400</v>
       </c>
       <c r="J94" s="3">
-        <v>14600</v>
+        <v>18800</v>
       </c>
       <c r="K94" s="3">
         <v>-28700</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>61200</v>
+        <v>61600</v>
       </c>
       <c r="E100" s="3">
-        <v>20900</v>
+        <v>21300</v>
       </c>
       <c r="F100" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="G100" s="3">
-        <v>6400</v>
+        <v>7300</v>
       </c>
       <c r="H100" s="3">
-        <v>-4000</v>
+        <v>-4400</v>
       </c>
       <c r="I100" s="3">
-        <v>34600</v>
+        <v>41900</v>
       </c>
       <c r="J100" s="3">
-        <v>6900</v>
+        <v>8900</v>
       </c>
       <c r="K100" s="3">
         <v>61900</v>
@@ -4460,16 +4460,16 @@
         <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I101" s="3">
-        <v>2200</v>
+        <v>2700</v>
       </c>
       <c r="J101" s="3">
         <v>200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14800</v>
+        <v>15500</v>
       </c>
       <c r="E102" s="3">
-        <v>-3500</v>
+        <v>-3600</v>
       </c>
       <c r="F102" s="3">
-        <v>-10900</v>
+        <v>-12000</v>
       </c>
       <c r="G102" s="3">
-        <v>12700</v>
+        <v>14600</v>
       </c>
       <c r="H102" s="3">
-        <v>-8600</v>
+        <v>-9500</v>
       </c>
       <c r="I102" s="3">
-        <v>-13100</v>
+        <v>-15900</v>
       </c>
       <c r="J102" s="3">
-        <v>11100</v>
+        <v>14300</v>
       </c>
       <c r="K102" s="3">
         <v>13800</v>

--- a/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YTRA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>YTRA</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41730</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E8" s="3">
         <v>50300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>96400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>135100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>188200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>112800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>100900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>84300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E9" s="3">
         <v>27200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>63500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>121800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>50400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>50300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E10" s="3">
         <v>23100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>62400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,41 +981,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>51200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1010,54 +1029,60 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E17" s="3">
         <v>53400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>107900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>165700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>235400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>186500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>115500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>97100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-47100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-73600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-22300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-49700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-66800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-61400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-71100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12800</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
       </c>
       <c r="H24" s="3">
         <v>900</v>
       </c>
       <c r="I24" s="3">
+        <v>900</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-62300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-71600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-61400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-71200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>22300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-61400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-71200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-61400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-71200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41730</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,143 +2074,153 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E41" s="3">
         <v>20900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E42" s="3">
         <v>31500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16800</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E43" s="3">
         <v>60200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>80500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>66800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2145,257 +2240,275 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
-      </c>
-      <c r="L44" s="3">
-        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E45" s="3">
         <v>18300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E46" s="3">
         <v>131600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>66700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>81000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>140300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>136000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>91900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48200</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>300</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E49" s="3">
         <v>11000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>34200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3400</v>
       </c>
       <c r="H52" s="3">
         <v>3400</v>
       </c>
       <c r="I52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J52" s="3">
         <v>4200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E54" s="3">
         <v>149900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>181200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>178500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>60500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,233 +2786,249 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>76000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>38000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E58" s="3">
         <v>6900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>29000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E59" s="3">
         <v>24100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E60" s="3">
         <v>52700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>143200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>165300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>70300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>42200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2893,42 +3038,45 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
       <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E66" s="3">
         <v>56800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>96200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>146800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>182000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>77600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-238400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-243200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-242600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-258500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-262000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-239800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-249100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-245900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-135900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-70700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-61300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-54500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E76" s="3">
         <v>64700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41730</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-61400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-71200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
       </c>
       <c r="F83" s="3">
+        <v>900</v>
+      </c>
+      <c r="G83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-51100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-800</v>
       </c>
       <c r="L91" s="3">
         <v>-800</v>
       </c>
       <c r="M91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>18800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E100" s="3">
         <v>61600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>61900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>15500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
